--- a/intermedios/03_enlistamiento/01_concistencia/202412/20242911.xlsx
+++ b/intermedios/03_enlistamiento/01_concistencia/202412/20242911.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="435">
   <si>
     <t>pro</t>
   </si>
@@ -1663,6 +1663,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="48" max="48" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2294,8 +2297,8 @@
       <c r="AU5" t="s">
         <v>125</v>
       </c>
-      <c r="AV5" t="s">
-        <v>145</v>
+      <c r="AV5">
+        <v>40350999006</v>
       </c>
       <c r="AW5" t="s">
         <v>58</v>
